--- a/Excel/CrystalPools.xlsx
+++ b/Excel/CrystalPools.xlsx
@@ -5,17 +5,24 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnyan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c3f59aaaf5f4e1f8/Desktop/Data-analysis/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F98566-C7CE-46D1-8C59-01370A072AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{09F98566-C7CE-46D1-8C59-01370A072AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74C2E363-92FD-4BFE-816B-FC52FC0138A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sales" sheetId="1" r:id="rId1"/>
+    <sheet name="pivot table and Pie chart" sheetId="2" r:id="rId1"/>
+    <sheet name="Sales" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sales!$A$1:$L$172</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="60">
   <si>
     <t>Product Code</t>
   </si>
@@ -185,6 +192,36 @@
   <si>
     <t>Sum of items valued at 50$ or less</t>
   </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>sumif</t>
+  </si>
+  <si>
+    <t>filter</t>
+  </si>
+  <si>
+    <t>pivot table</t>
+  </si>
+  <si>
+    <t>pie chart</t>
+  </si>
+  <si>
+    <t>summarize a large group of data</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Sale Price</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
 </sst>
 </file>
 
@@ -195,7 +232,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -230,6 +267,13 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
@@ -300,7 +344,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -311,6 +355,11 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -370,6 +419,5615 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[CrystalPools.xlsx]pivot table and Pie chart!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="24"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="25"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12478019276516056"/>
+          <c:y val="0.16564596092155148"/>
+          <c:w val="0.70270691886654668"/>
+          <c:h val="0.75010279965004378"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'pivot table and Pie chart'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'pivot table and Pie chart'!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Barns</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Smith</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Johnson</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hernandez</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'pivot table and Pie chart'!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6003.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5661.0999999999985</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3035.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2410.7000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-13D6-42E0-A365-DB22DB70B566}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1757576080"/>
+        <c:axId val="1757560720"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1757576080"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1757560720"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1757560720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1757576080"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[CrystalPools.xlsx]pivot table and Pie chart!PivotTable1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="25400">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d contourW="25400">
+            <a:contourClr>
+              <a:schemeClr val="lt1"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'pivot table and Pie chart'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'pivot table and Pie chart'!$A$4:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Barns</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Smith</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Johnson</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Hernandez</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'pivot table and Pie chart'!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6003.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5661.0999999999985</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3035.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2410.7000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BFA1-41C3-8CC7-9E0C4FF347BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>613410</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8A6250-93B8-9457-1AD4-D66C6303A825}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08162686-63AB-30BC-CF40-28C7DD55B7A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Dnyaneshwari Katkar" refreshedDate="46228.70657800926" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="171" xr:uid="{A21E3E2D-02DF-4F95-9FFC-2B9104A7FCE2}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K172" sheet="Sales"/>
+  </cacheSource>
+  <cacheFields count="11">
+    <cacheField name="Month" numFmtId="14">
+      <sharedItems count="12">
+        <s v="Jan"/>
+        <s v="Feb"/>
+        <s v="Mar"/>
+        <s v="April"/>
+        <s v="May"/>
+        <s v="June"/>
+        <s v="July"/>
+        <s v="Aug"/>
+        <s v="Sept"/>
+        <s v="Oct"/>
+        <s v="Nov"/>
+        <s v="Dec"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Transaction Number" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1171"/>
+    </cacheField>
+    <cacheField name="Product Code" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1109" maxValue="9822"/>
+    </cacheField>
+    <cacheField name="Product Description" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Store Cost" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3" maxValue="344"/>
+    </cacheField>
+    <cacheField name="Sale Price" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7" maxValue="502" count="10">
+        <n v="98.4"/>
+        <n v="16.3"/>
+        <n v="9.1999999999999993"/>
+        <n v="502"/>
+        <n v="8"/>
+        <n v="87"/>
+        <n v="7"/>
+        <n v="124"/>
+        <n v="14"/>
+        <n v="77"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Profit" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.9999999999999991" maxValue="158"/>
+    </cacheField>
+    <cacheField name="Commision 10% for items less than $50. 20% for items more than $50" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.29999999999999993" maxValue="31.6"/>
+    </cacheField>
+    <cacheField name="First Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Last Name" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Barns"/>
+        <s v="Hernandez"/>
+        <s v="Smith"/>
+        <s v="Johnson"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sale Location" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="171">
+  <r>
+    <x v="0"/>
+    <n v="1001"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1002"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1003"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1004"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1005"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1006"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1007"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1008"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1009"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1010"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1011"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1012"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1013"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1014"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1015"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <n v="1016"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1017"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1018"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1019"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1020"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1021"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1022"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1023"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1024"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1025"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1026"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1027"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1028"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1029"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1030"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1031"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1032"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1033"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="1034"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1035"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1036"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1037"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1038"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1039"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1040"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1041"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1042"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1043"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1044"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1045"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1046"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1047"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="1048"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1049"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CO"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1050"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1051"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1052"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1053"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1054"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1055"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1056"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1057"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1058"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1059"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="1060"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1061"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1062"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1063"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1064"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1065"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1066"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1067"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1068"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1069"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1070"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1071"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1072"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1073"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1074"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1075"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1076"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1077"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <n v="1078"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1079"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1080"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1081"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1082"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1083"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1084"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1085"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1086"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1087"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1088"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1089"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1090"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1091"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1092"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1093"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1094"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1095"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1096"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1097"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <n v="1098"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1099"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1100"/>
+    <n v="6119"/>
+    <s v="Algea Killer 8 oz"/>
+    <n v="9"/>
+    <x v="8"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1101"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1102"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1103"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1104"/>
+    <n v="2877"/>
+    <s v="Net"/>
+    <n v="11.4"/>
+    <x v="1"/>
+    <n v="4.9000000000000004"/>
+    <n v="0.49000000000000005"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1105"/>
+    <n v="2499"/>
+    <s v="8 ft Hose"/>
+    <n v="6.2"/>
+    <x v="2"/>
+    <n v="2.9999999999999991"/>
+    <n v="0.29999999999999993"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1106"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1107"/>
+    <n v="1109"/>
+    <s v="Chlorine Test Kit"/>
+    <n v="3"/>
+    <x v="4"/>
+    <n v="5"/>
+    <n v="0.5"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1108"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1109"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1110"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1111"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1112"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1113"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1114"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1115"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1116"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1117"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1118"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1119"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1120"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1121"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1122"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1123"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <n v="1124"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1125"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1126"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1127"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1128"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1129"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1130"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1131"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1132"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1133"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1134"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1135"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1136"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1137"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1138"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1139"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1140"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <n v="1141"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1142"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1143"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1144"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1145"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1146"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1147"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1148"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <n v="1149"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1150"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1151"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1152"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1153"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1154"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1155"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1156"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <n v="1157"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1158"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1159"/>
+    <n v="6622"/>
+    <s v="5 Gal Chlorine"/>
+    <n v="42"/>
+    <x v="9"/>
+    <n v="35"/>
+    <n v="7"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1160"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Hellen"/>
+    <x v="3"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1161"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1162"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1163"/>
+    <n v="9212"/>
+    <s v="1 Gal Muratic Acid"/>
+    <n v="4"/>
+    <x v="6"/>
+    <n v="3"/>
+    <n v="0.30000000000000004"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1164"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1165"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="AZ"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <n v="1166"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NV"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1167"/>
+    <n v="2242"/>
+    <s v="AutoVac"/>
+    <n v="60"/>
+    <x v="7"/>
+    <n v="64"/>
+    <n v="12.8"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="NM"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1168"/>
+    <n v="9822"/>
+    <s v="Pool Cover"/>
+    <n v="58.3"/>
+    <x v="0"/>
+    <n v="40.100000000000009"/>
+    <n v="8.0200000000000014"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1169"/>
+    <n v="8722"/>
+    <s v="Water Pump"/>
+    <n v="344"/>
+    <x v="3"/>
+    <n v="158"/>
+    <n v="31.6"/>
+    <s v="Doug"/>
+    <x v="2"/>
+    <s v="UT"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1170"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Chalie"/>
+    <x v="0"/>
+    <s v="CA"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <n v="1171"/>
+    <n v="4421"/>
+    <s v="Skimmer"/>
+    <n v="45"/>
+    <x v="5"/>
+    <n v="42"/>
+    <n v="8.4"/>
+    <s v="Juan"/>
+    <x v="1"/>
+    <s v="NV"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0204216-96B3-475C-88F1-27393AC4386C}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0">
+      <items count="11">
+        <item x="6"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Sale Price" fld="5" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <chartFormats count="13">
+    <chartFormat chart="0" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="16" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="18" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="19" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="20" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="21" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="22" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="23" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="24" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="25" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -693,11 +6351,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669C4A76-7828-40D1-A93B-C836764FB0C8}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="8">
+        <v>6003.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="8">
+        <v>5661.0999999999985</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="8">
+        <v>3035.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="8">
+        <v>2410.7000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="8">
+        <v>17110.599999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.59765625" bestFit="1" customWidth="1"/>
@@ -800,11 +6536,11 @@
         <v>16.3</v>
       </c>
       <c r="G3" s="4">
-        <f t="shared" ref="G3:G66" si="0">F3-E3</f>
+        <f>F3-E3</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H66" si="1">IF(F3&gt;50,G3*0.2,G3*0.1)</f>
+        <f>IF(F3&gt;50,G3*0.2,G3*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I3" t="s">
@@ -837,11 +6573,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
+        <f>F4-E4</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
+        <f>IF(F4&gt;50,G4*0.2,G4*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I4" t="s">
@@ -874,11 +6610,11 @@
         <v>502</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" si="0"/>
+        <f>F5-E5</f>
         <v>158</v>
       </c>
       <c r="H5">
-        <f t="shared" si="1"/>
+        <f>IF(F5&gt;50,G5*0.2,G5*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I5" t="s">
@@ -911,11 +6647,11 @@
         <v>8</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="0"/>
+        <f>F6-E6</f>
         <v>5</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
+        <f>IF(F6&gt;50,G6*0.2,G6*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I6" t="s">
@@ -948,11 +6684,11 @@
         <v>98.4</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" si="0"/>
+        <f>F7-E7</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H7">
-        <f t="shared" si="1"/>
+        <f>IF(F7&gt;50,G7*0.2,G7*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I7" t="s">
@@ -985,11 +6721,11 @@
         <v>8</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
+        <f>F8-E8</f>
         <v>5</v>
       </c>
       <c r="H8">
-        <f t="shared" si="1"/>
+        <f>IF(F8&gt;50,G8*0.2,G8*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I8" t="s">
@@ -1022,11 +6758,11 @@
         <v>16.3</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
+        <f>F9-E9</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H9">
-        <f t="shared" si="1"/>
+        <f>IF(F9&gt;50,G9*0.2,G9*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I9" t="s">
@@ -1059,11 +6795,11 @@
         <v>8</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
+        <f>F10-E10</f>
         <v>5</v>
       </c>
       <c r="H10">
-        <f t="shared" si="1"/>
+        <f>IF(F10&gt;50,G10*0.2,G10*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I10" t="s">
@@ -1096,11 +6832,11 @@
         <v>16.3</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
+        <f>F11-E11</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H11">
-        <f t="shared" si="1"/>
+        <f>IF(F11&gt;50,G11*0.2,G11*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I11" t="s">
@@ -1133,11 +6869,11 @@
         <v>16.3</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
+        <f>F12-E12</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H12">
-        <f t="shared" si="1"/>
+        <f>IF(F12&gt;50,G12*0.2,G12*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I12" t="s">
@@ -1170,11 +6906,11 @@
         <v>87</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
+        <f>F13-E13</f>
         <v>42</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
+        <f>IF(F13&gt;50,G13*0.2,G13*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I13" t="s">
@@ -1207,11 +6943,11 @@
         <v>7</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="0"/>
+        <f>F14-E14</f>
         <v>3</v>
       </c>
       <c r="H14">
-        <f t="shared" si="1"/>
+        <f>IF(F14&gt;50,G14*0.2,G14*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I14" t="s">
@@ -1244,11 +6980,11 @@
         <v>502</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="0"/>
+        <f>F15-E15</f>
         <v>158</v>
       </c>
       <c r="H15">
-        <f t="shared" si="1"/>
+        <f>IF(F15&gt;50,G15*0.2,G15*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I15" t="s">
@@ -1281,11 +7017,11 @@
         <v>16.3</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
+        <f>F16-E16</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H16">
-        <f t="shared" si="1"/>
+        <f>IF(F16&gt;50,G16*0.2,G16*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I16" t="s">
@@ -1318,11 +7054,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="0"/>
+        <f>F17-E17</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H17">
-        <f t="shared" si="1"/>
+        <f>IF(F17&gt;50,G17*0.2,G17*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I17" t="s">
@@ -1355,11 +7091,11 @@
         <v>124</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="0"/>
+        <f>F18-E18</f>
         <v>64</v>
       </c>
       <c r="H18">
-        <f t="shared" si="1"/>
+        <f>IF(F18&gt;50,G18*0.2,G18*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I18" t="s">
@@ -1392,11 +7128,11 @@
         <v>8</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="0"/>
+        <f>F19-E19</f>
         <v>5</v>
       </c>
       <c r="H19">
-        <f t="shared" si="1"/>
+        <f>IF(F19&gt;50,G19*0.2,G19*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I19" t="s">
@@ -1429,11 +7165,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="0"/>
+        <f>F20-E20</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H20">
-        <f t="shared" si="1"/>
+        <f>IF(F20&gt;50,G20*0.2,G20*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I20" t="s">
@@ -1466,11 +7202,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="0"/>
+        <f>F21-E21</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H21">
-        <f t="shared" si="1"/>
+        <f>IF(F21&gt;50,G21*0.2,G21*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I21" t="s">
@@ -1503,11 +7239,11 @@
         <v>8</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="0"/>
+        <f>F22-E22</f>
         <v>5</v>
       </c>
       <c r="H22">
-        <f t="shared" si="1"/>
+        <f>IF(F22&gt;50,G22*0.2,G22*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I22" t="s">
@@ -1540,11 +7276,11 @@
         <v>16.3</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="0"/>
+        <f>F23-E23</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H23">
-        <f t="shared" si="1"/>
+        <f>IF(F23&gt;50,G23*0.2,G23*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I23" t="s">
@@ -1577,11 +7313,11 @@
         <v>8</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="0"/>
+        <f>F24-E24</f>
         <v>5</v>
       </c>
       <c r="H24">
-        <f t="shared" si="1"/>
+        <f>IF(F24&gt;50,G24*0.2,G24*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I24" t="s">
@@ -1614,11 +7350,11 @@
         <v>7</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="0"/>
+        <f>F25-E25</f>
         <v>3</v>
       </c>
       <c r="H25">
-        <f t="shared" si="1"/>
+        <f>IF(F25&gt;50,G25*0.2,G25*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I25" t="s">
@@ -1651,11 +7387,11 @@
         <v>16.3</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="0"/>
+        <f>F26-E26</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H26">
-        <f t="shared" si="1"/>
+        <f>IF(F26&gt;50,G26*0.2,G26*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I26" t="s">
@@ -1688,11 +7424,11 @@
         <v>14</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" si="0"/>
+        <f>F27-E27</f>
         <v>5</v>
       </c>
       <c r="H27">
-        <f t="shared" si="1"/>
+        <f>IF(F27&gt;50,G27*0.2,G27*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I27" t="s">
@@ -1725,11 +7461,11 @@
         <v>14</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" si="0"/>
+        <f>F28-E28</f>
         <v>5</v>
       </c>
       <c r="H28">
-        <f t="shared" si="1"/>
+        <f>IF(F28&gt;50,G28*0.2,G28*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I28" t="s">
@@ -1762,11 +7498,11 @@
         <v>502</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" si="0"/>
+        <f>F29-E29</f>
         <v>158</v>
       </c>
       <c r="H29">
-        <f t="shared" si="1"/>
+        <f>IF(F29&gt;50,G29*0.2,G29*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I29" t="s">
@@ -1799,11 +7535,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G30" s="4">
-        <f t="shared" si="0"/>
+        <f>F30-E30</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H30">
-        <f t="shared" si="1"/>
+        <f>IF(F30&gt;50,G30*0.2,G30*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I30" t="s">
@@ -1836,11 +7572,11 @@
         <v>87</v>
       </c>
       <c r="G31" s="4">
-        <f t="shared" si="0"/>
+        <f>F31-E31</f>
         <v>42</v>
       </c>
       <c r="H31">
-        <f t="shared" si="1"/>
+        <f>IF(F31&gt;50,G31*0.2,G31*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I31" t="s">
@@ -1873,11 +7609,11 @@
         <v>8</v>
       </c>
       <c r="G32" s="4">
-        <f t="shared" si="0"/>
+        <f>F32-E32</f>
         <v>5</v>
       </c>
       <c r="H32">
-        <f t="shared" si="1"/>
+        <f>IF(F32&gt;50,G32*0.2,G32*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I32" t="s">
@@ -1910,11 +7646,11 @@
         <v>16.3</v>
       </c>
       <c r="G33" s="4">
-        <f t="shared" si="0"/>
+        <f>F33-E33</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H33">
-        <f t="shared" si="1"/>
+        <f>IF(F33&gt;50,G33*0.2,G33*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I33" t="s">
@@ -1947,11 +7683,11 @@
         <v>98.4</v>
       </c>
       <c r="G34" s="4">
-        <f t="shared" si="0"/>
+        <f>F34-E34</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H34">
-        <f t="shared" si="1"/>
+        <f>IF(F34&gt;50,G34*0.2,G34*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I34" t="s">
@@ -1984,11 +7720,11 @@
         <v>16.3</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" si="0"/>
+        <f>F35-E35</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H35">
-        <f t="shared" si="1"/>
+        <f>IF(F35&gt;50,G35*0.2,G35*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I35" t="s">
@@ -2021,11 +7757,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" si="0"/>
+        <f>F36-E36</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H36">
-        <f t="shared" si="1"/>
+        <f>IF(F36&gt;50,G36*0.2,G36*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I36" t="s">
@@ -2058,11 +7794,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" si="0"/>
+        <f>F37-E37</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H37">
-        <f t="shared" si="1"/>
+        <f>IF(F37&gt;50,G37*0.2,G37*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I37" t="s">
@@ -2095,11 +7831,11 @@
         <v>77</v>
       </c>
       <c r="G38" s="4">
-        <f t="shared" si="0"/>
+        <f>F38-E38</f>
         <v>35</v>
       </c>
       <c r="H38">
-        <f t="shared" si="1"/>
+        <f>IF(F38&gt;50,G38*0.2,G38*0.1)</f>
         <v>7</v>
       </c>
       <c r="I38" t="s">
@@ -2132,11 +7868,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G39" s="4">
-        <f t="shared" si="0"/>
+        <f>F39-E39</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H39">
-        <f t="shared" si="1"/>
+        <f>IF(F39&gt;50,G39*0.2,G39*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I39" t="s">
@@ -2169,11 +7905,11 @@
         <v>16.3</v>
       </c>
       <c r="G40" s="4">
-        <f t="shared" si="0"/>
+        <f>F40-E40</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H40">
-        <f t="shared" si="1"/>
+        <f>IF(F40&gt;50,G40*0.2,G40*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I40" t="s">
@@ -2206,11 +7942,11 @@
         <v>8</v>
       </c>
       <c r="G41" s="4">
-        <f t="shared" si="0"/>
+        <f>F41-E41</f>
         <v>5</v>
       </c>
       <c r="H41">
-        <f t="shared" si="1"/>
+        <f>IF(F41&gt;50,G41*0.2,G41*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I41" t="s">
@@ -2243,11 +7979,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G42" s="4">
-        <f t="shared" si="0"/>
+        <f>F42-E42</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H42">
-        <f t="shared" si="1"/>
+        <f>IF(F42&gt;50,G42*0.2,G42*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I42" t="s">
@@ -2280,11 +8016,11 @@
         <v>502</v>
       </c>
       <c r="G43" s="4">
-        <f t="shared" si="0"/>
+        <f>F43-E43</f>
         <v>158</v>
       </c>
       <c r="H43">
-        <f t="shared" si="1"/>
+        <f>IF(F43&gt;50,G43*0.2,G43*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I43" t="s">
@@ -2317,11 +8053,11 @@
         <v>124</v>
       </c>
       <c r="G44" s="4">
-        <f t="shared" si="0"/>
+        <f>F44-E44</f>
         <v>64</v>
       </c>
       <c r="H44">
-        <f t="shared" si="1"/>
+        <f>IF(F44&gt;50,G44*0.2,G44*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I44" t="s">
@@ -2354,11 +8090,11 @@
         <v>16.3</v>
       </c>
       <c r="G45" s="4">
-        <f t="shared" si="0"/>
+        <f>F45-E45</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H45">
-        <f t="shared" si="1"/>
+        <f>IF(F45&gt;50,G45*0.2,G45*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I45" t="s">
@@ -2391,11 +8127,11 @@
         <v>502</v>
       </c>
       <c r="G46" s="4">
-        <f t="shared" si="0"/>
+        <f>F46-E46</f>
         <v>158</v>
       </c>
       <c r="H46">
-        <f t="shared" si="1"/>
+        <f>IF(F46&gt;50,G46*0.2,G46*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I46" t="s">
@@ -2428,11 +8164,11 @@
         <v>14</v>
       </c>
       <c r="G47" s="4">
-        <f t="shared" si="0"/>
+        <f>F47-E47</f>
         <v>5</v>
       </c>
       <c r="H47">
-        <f t="shared" si="1"/>
+        <f>IF(F47&gt;50,G47*0.2,G47*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I47" t="s">
@@ -2465,11 +8201,11 @@
         <v>77</v>
       </c>
       <c r="G48" s="4">
-        <f t="shared" si="0"/>
+        <f>F48-E48</f>
         <v>35</v>
       </c>
       <c r="H48">
-        <f t="shared" si="1"/>
+        <f>IF(F48&gt;50,G48*0.2,G48*0.1)</f>
         <v>7</v>
       </c>
       <c r="I48" t="s">
@@ -2502,11 +8238,11 @@
         <v>502</v>
       </c>
       <c r="G49" s="4">
-        <f t="shared" si="0"/>
+        <f>F49-E49</f>
         <v>158</v>
       </c>
       <c r="H49">
-        <f t="shared" si="1"/>
+        <f>IF(F49&gt;50,G49*0.2,G49*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I49" t="s">
@@ -2539,11 +8275,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" si="0"/>
+        <f>F50-E50</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H50">
-        <f t="shared" si="1"/>
+        <f>IF(F50&gt;50,G50*0.2,G50*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I50" t="s">
@@ -2576,11 +8312,11 @@
         <v>16.3</v>
       </c>
       <c r="G51" s="4">
-        <f t="shared" si="0"/>
+        <f>F51-E51</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H51">
-        <f t="shared" si="1"/>
+        <f>IF(F51&gt;50,G51*0.2,G51*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I51" t="s">
@@ -2613,11 +8349,11 @@
         <v>14</v>
       </c>
       <c r="G52" s="4">
-        <f t="shared" si="0"/>
+        <f>F52-E52</f>
         <v>5</v>
       </c>
       <c r="H52">
-        <f t="shared" si="1"/>
+        <f>IF(F52&gt;50,G52*0.2,G52*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I52" t="s">
@@ -2650,11 +8386,11 @@
         <v>77</v>
       </c>
       <c r="G53" s="4">
-        <f t="shared" si="0"/>
+        <f>F53-E53</f>
         <v>35</v>
       </c>
       <c r="H53">
-        <f t="shared" si="1"/>
+        <f>IF(F53&gt;50,G53*0.2,G53*0.1)</f>
         <v>7</v>
       </c>
       <c r="I53" t="s">
@@ -2687,11 +8423,11 @@
         <v>124</v>
       </c>
       <c r="G54" s="4">
-        <f t="shared" si="0"/>
+        <f>F54-E54</f>
         <v>64</v>
       </c>
       <c r="H54">
-        <f t="shared" si="1"/>
+        <f>IF(F54&gt;50,G54*0.2,G54*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I54" t="s">
@@ -2724,11 +8460,11 @@
         <v>87</v>
       </c>
       <c r="G55" s="4">
-        <f t="shared" si="0"/>
+        <f>F55-E55</f>
         <v>42</v>
       </c>
       <c r="H55">
-        <f t="shared" si="1"/>
+        <f>IF(F55&gt;50,G55*0.2,G55*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I55" t="s">
@@ -2761,11 +8497,11 @@
         <v>14</v>
       </c>
       <c r="G56" s="4">
-        <f t="shared" si="0"/>
+        <f>F56-E56</f>
         <v>5</v>
       </c>
       <c r="H56">
-        <f t="shared" si="1"/>
+        <f>IF(F56&gt;50,G56*0.2,G56*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I56" t="s">
@@ -2798,11 +8534,11 @@
         <v>8</v>
       </c>
       <c r="G57" s="4">
-        <f t="shared" si="0"/>
+        <f>F57-E57</f>
         <v>5</v>
       </c>
       <c r="H57">
-        <f t="shared" si="1"/>
+        <f>IF(F57&gt;50,G57*0.2,G57*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I57" t="s">
@@ -2835,11 +8571,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G58" s="4">
-        <f t="shared" si="0"/>
+        <f>F58-E58</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H58">
-        <f t="shared" si="1"/>
+        <f>IF(F58&gt;50,G58*0.2,G58*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I58" t="s">
@@ -2872,11 +8608,11 @@
         <v>14</v>
       </c>
       <c r="G59" s="4">
-        <f t="shared" si="0"/>
+        <f>F59-E59</f>
         <v>5</v>
       </c>
       <c r="H59">
-        <f t="shared" si="1"/>
+        <f>IF(F59&gt;50,G59*0.2,G59*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I59" t="s">
@@ -2909,11 +8645,11 @@
         <v>124</v>
       </c>
       <c r="G60" s="4">
-        <f t="shared" si="0"/>
+        <f>F60-E60</f>
         <v>64</v>
       </c>
       <c r="H60">
-        <f t="shared" si="1"/>
+        <f>IF(F60&gt;50,G60*0.2,G60*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I60" t="s">
@@ -2946,11 +8682,11 @@
         <v>14</v>
       </c>
       <c r="G61" s="4">
-        <f t="shared" si="0"/>
+        <f>F61-E61</f>
         <v>5</v>
       </c>
       <c r="H61">
-        <f t="shared" si="1"/>
+        <f>IF(F61&gt;50,G61*0.2,G61*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I61" t="s">
@@ -2983,11 +8719,11 @@
         <v>8</v>
       </c>
       <c r="G62" s="4">
-        <f t="shared" si="0"/>
+        <f>F62-E62</f>
         <v>5</v>
       </c>
       <c r="H62">
-        <f t="shared" si="1"/>
+        <f>IF(F62&gt;50,G62*0.2,G62*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I62" t="s">
@@ -3020,11 +8756,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G63" s="4">
-        <f t="shared" si="0"/>
+        <f>F63-E63</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H63">
-        <f t="shared" si="1"/>
+        <f>IF(F63&gt;50,G63*0.2,G63*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I63" t="s">
@@ -3057,11 +8793,11 @@
         <v>8</v>
       </c>
       <c r="G64" s="4">
-        <f t="shared" si="0"/>
+        <f>F64-E64</f>
         <v>5</v>
       </c>
       <c r="H64">
-        <f t="shared" si="1"/>
+        <f>IF(F64&gt;50,G64*0.2,G64*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I64" t="s">
@@ -3094,11 +8830,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G65" s="4">
-        <f t="shared" si="0"/>
+        <f>F65-E65</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H65">
-        <f t="shared" si="1"/>
+        <f>IF(F65&gt;50,G65*0.2,G65*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I65" t="s">
@@ -3131,11 +8867,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G66" s="4">
-        <f t="shared" si="0"/>
+        <f>F66-E66</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H66">
-        <f t="shared" si="1"/>
+        <f>IF(F66&gt;50,G66*0.2,G66*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I66" t="s">
@@ -3168,11 +8904,11 @@
         <v>16.3</v>
       </c>
       <c r="G67" s="4">
-        <f t="shared" ref="G67:G130" si="2">F67-E67</f>
+        <f>F67-E67</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H67">
-        <f t="shared" ref="H67:H130" si="3">IF(F67&gt;50,G67*0.2,G67*0.1)</f>
+        <f>IF(F67&gt;50,G67*0.2,G67*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I67" t="s">
@@ -3205,11 +8941,11 @@
         <v>16.3</v>
       </c>
       <c r="G68" s="4">
-        <f t="shared" si="2"/>
+        <f>F68-E68</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H68">
-        <f t="shared" si="3"/>
+        <f>IF(F68&gt;50,G68*0.2,G68*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I68" t="s">
@@ -3242,11 +8978,11 @@
         <v>14</v>
       </c>
       <c r="G69" s="4">
-        <f t="shared" si="2"/>
+        <f>F69-E69</f>
         <v>5</v>
       </c>
       <c r="H69">
-        <f t="shared" si="3"/>
+        <f>IF(F69&gt;50,G69*0.2,G69*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I69" t="s">
@@ -3279,11 +9015,11 @@
         <v>8</v>
       </c>
       <c r="G70" s="4">
-        <f t="shared" si="2"/>
+        <f>F70-E70</f>
         <v>5</v>
       </c>
       <c r="H70">
-        <f t="shared" si="3"/>
+        <f>IF(F70&gt;50,G70*0.2,G70*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I70" t="s">
@@ -3316,11 +9052,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G71" s="4">
-        <f t="shared" si="2"/>
+        <f>F71-E71</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H71">
-        <f t="shared" si="3"/>
+        <f>IF(F71&gt;50,G71*0.2,G71*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I71" t="s">
@@ -3353,11 +9089,11 @@
         <v>8</v>
       </c>
       <c r="G72" s="4">
-        <f t="shared" si="2"/>
+        <f>F72-E72</f>
         <v>5</v>
       </c>
       <c r="H72">
-        <f t="shared" si="3"/>
+        <f>IF(F72&gt;50,G72*0.2,G72*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I72" t="s">
@@ -3390,11 +9126,11 @@
         <v>8</v>
       </c>
       <c r="G73" s="4">
-        <f t="shared" si="2"/>
+        <f>F73-E73</f>
         <v>5</v>
       </c>
       <c r="H73">
-        <f t="shared" si="3"/>
+        <f>IF(F73&gt;50,G73*0.2,G73*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I73" t="s">
@@ -3427,11 +9163,11 @@
         <v>77</v>
       </c>
       <c r="G74" s="4">
-        <f t="shared" si="2"/>
+        <f>F74-E74</f>
         <v>35</v>
       </c>
       <c r="H74">
-        <f t="shared" si="3"/>
+        <f>IF(F74&gt;50,G74*0.2,G74*0.1)</f>
         <v>7</v>
       </c>
       <c r="I74" t="s">
@@ -3464,11 +9200,11 @@
         <v>16.3</v>
       </c>
       <c r="G75" s="4">
-        <f t="shared" si="2"/>
+        <f>F75-E75</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H75">
-        <f t="shared" si="3"/>
+        <f>IF(F75&gt;50,G75*0.2,G75*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I75" t="s">
@@ -3501,11 +9237,11 @@
         <v>8</v>
       </c>
       <c r="G76" s="4">
-        <f t="shared" si="2"/>
+        <f>F76-E76</f>
         <v>5</v>
       </c>
       <c r="H76">
-        <f t="shared" si="3"/>
+        <f>IF(F76&gt;50,G76*0.2,G76*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I76" t="s">
@@ -3538,11 +9274,11 @@
         <v>8</v>
       </c>
       <c r="G77" s="4">
-        <f t="shared" si="2"/>
+        <f>F77-E77</f>
         <v>5</v>
       </c>
       <c r="H77">
-        <f t="shared" si="3"/>
+        <f>IF(F77&gt;50,G77*0.2,G77*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I77" t="s">
@@ -3575,11 +9311,11 @@
         <v>98.4</v>
       </c>
       <c r="G78" s="4">
-        <f t="shared" si="2"/>
+        <f>F78-E78</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H78">
-        <f t="shared" si="3"/>
+        <f>IF(F78&gt;50,G78*0.2,G78*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I78" t="s">
@@ -3612,11 +9348,11 @@
         <v>16.3</v>
       </c>
       <c r="G79" s="4">
-        <f t="shared" si="2"/>
+        <f>F79-E79</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H79">
-        <f t="shared" si="3"/>
+        <f>IF(F79&gt;50,G79*0.2,G79*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I79" t="s">
@@ -3649,11 +9385,11 @@
         <v>16.3</v>
       </c>
       <c r="G80" s="4">
-        <f t="shared" si="2"/>
+        <f>F80-E80</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H80">
-        <f t="shared" si="3"/>
+        <f>IF(F80&gt;50,G80*0.2,G80*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I80" t="s">
@@ -3686,11 +9422,11 @@
         <v>87</v>
       </c>
       <c r="G81" s="4">
-        <f t="shared" si="2"/>
+        <f>F81-E81</f>
         <v>42</v>
       </c>
       <c r="H81">
-        <f t="shared" si="3"/>
+        <f>IF(F81&gt;50,G81*0.2,G81*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I81" t="s">
@@ -3723,11 +9459,11 @@
         <v>14</v>
       </c>
       <c r="G82" s="4">
-        <f t="shared" si="2"/>
+        <f>F82-E82</f>
         <v>5</v>
       </c>
       <c r="H82">
-        <f t="shared" si="3"/>
+        <f>IF(F82&gt;50,G82*0.2,G82*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I82" t="s">
@@ -3760,11 +9496,11 @@
         <v>8</v>
       </c>
       <c r="G83" s="4">
-        <f t="shared" si="2"/>
+        <f>F83-E83</f>
         <v>5</v>
       </c>
       <c r="H83">
-        <f t="shared" si="3"/>
+        <f>IF(F83&gt;50,G83*0.2,G83*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I83" t="s">
@@ -3797,11 +9533,11 @@
         <v>8</v>
       </c>
       <c r="G84" s="4">
-        <f t="shared" si="2"/>
+        <f>F84-E84</f>
         <v>5</v>
       </c>
       <c r="H84">
-        <f t="shared" si="3"/>
+        <f>IF(F84&gt;50,G84*0.2,G84*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I84" t="s">
@@ -3834,11 +9570,11 @@
         <v>14</v>
       </c>
       <c r="G85" s="4">
-        <f t="shared" si="2"/>
+        <f>F85-E85</f>
         <v>5</v>
       </c>
       <c r="H85">
-        <f t="shared" si="3"/>
+        <f>IF(F85&gt;50,G85*0.2,G85*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I85" t="s">
@@ -3871,11 +9607,11 @@
         <v>98.4</v>
       </c>
       <c r="G86" s="4">
-        <f t="shared" si="2"/>
+        <f>F86-E86</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H86">
-        <f t="shared" si="3"/>
+        <f>IF(F86&gt;50,G86*0.2,G86*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I86" t="s">
@@ -3908,11 +9644,11 @@
         <v>8</v>
       </c>
       <c r="G87" s="4">
-        <f t="shared" si="2"/>
+        <f>F87-E87</f>
         <v>5</v>
       </c>
       <c r="H87">
-        <f t="shared" si="3"/>
+        <f>IF(F87&gt;50,G87*0.2,G87*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I87" t="s">
@@ -3945,11 +9681,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G88" s="4">
-        <f t="shared" si="2"/>
+        <f>F88-E88</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H88">
-        <f t="shared" si="3"/>
+        <f>IF(F88&gt;50,G88*0.2,G88*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I88" t="s">
@@ -3982,11 +9718,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G89" s="4">
-        <f t="shared" si="2"/>
+        <f>F89-E89</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H89">
-        <f t="shared" si="3"/>
+        <f>IF(F89&gt;50,G89*0.2,G89*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I89" t="s">
@@ -4019,11 +9755,11 @@
         <v>14</v>
       </c>
       <c r="G90" s="4">
-        <f t="shared" si="2"/>
+        <f>F90-E90</f>
         <v>5</v>
       </c>
       <c r="H90">
-        <f t="shared" si="3"/>
+        <f>IF(F90&gt;50,G90*0.2,G90*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I90" t="s">
@@ -4056,11 +9792,11 @@
         <v>16.3</v>
       </c>
       <c r="G91" s="4">
-        <f t="shared" si="2"/>
+        <f>F91-E91</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H91">
-        <f t="shared" si="3"/>
+        <f>IF(F91&gt;50,G91*0.2,G91*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I91" t="s">
@@ -4093,11 +9829,11 @@
         <v>16.3</v>
       </c>
       <c r="G92" s="4">
-        <f t="shared" si="2"/>
+        <f>F92-E92</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H92">
-        <f t="shared" si="3"/>
+        <f>IF(F92&gt;50,G92*0.2,G92*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I92" t="s">
@@ -4130,11 +9866,11 @@
         <v>16.3</v>
       </c>
       <c r="G93" s="4">
-        <f t="shared" si="2"/>
+        <f>F93-E93</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H93">
-        <f t="shared" si="3"/>
+        <f>IF(F93&gt;50,G93*0.2,G93*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I93" t="s">
@@ -4167,11 +9903,11 @@
         <v>14</v>
       </c>
       <c r="G94" s="4">
-        <f t="shared" si="2"/>
+        <f>F94-E94</f>
         <v>5</v>
       </c>
       <c r="H94">
-        <f t="shared" si="3"/>
+        <f>IF(F94&gt;50,G94*0.2,G94*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I94" t="s">
@@ -4204,11 +9940,11 @@
         <v>14</v>
       </c>
       <c r="G95" s="4">
-        <f t="shared" si="2"/>
+        <f>F95-E95</f>
         <v>5</v>
       </c>
       <c r="H95">
-        <f t="shared" si="3"/>
+        <f>IF(F95&gt;50,G95*0.2,G95*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I95" t="s">
@@ -4241,11 +9977,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G96" s="4">
-        <f t="shared" si="2"/>
+        <f>F96-E96</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H96">
-        <f t="shared" si="3"/>
+        <f>IF(F96&gt;50,G96*0.2,G96*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I96" t="s">
@@ -4278,11 +10014,11 @@
         <v>14</v>
       </c>
       <c r="G97" s="4">
-        <f t="shared" si="2"/>
+        <f>F97-E97</f>
         <v>5</v>
       </c>
       <c r="H97">
-        <f t="shared" si="3"/>
+        <f>IF(F97&gt;50,G97*0.2,G97*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I97" t="s">
@@ -4315,11 +10051,11 @@
         <v>7</v>
       </c>
       <c r="G98" s="4">
-        <f t="shared" si="2"/>
+        <f>F98-E98</f>
         <v>3</v>
       </c>
       <c r="H98">
-        <f t="shared" si="3"/>
+        <f>IF(F98&gt;50,G98*0.2,G98*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I98" t="s">
@@ -4352,11 +10088,11 @@
         <v>16.3</v>
       </c>
       <c r="G99" s="4">
-        <f t="shared" si="2"/>
+        <f>F99-E99</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H99">
-        <f t="shared" si="3"/>
+        <f>IF(F99&gt;50,G99*0.2,G99*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I99" t="s">
@@ -4389,11 +10125,11 @@
         <v>16.3</v>
       </c>
       <c r="G100" s="4">
-        <f t="shared" si="2"/>
+        <f>F100-E100</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H100">
-        <f t="shared" si="3"/>
+        <f>IF(F100&gt;50,G100*0.2,G100*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I100" t="s">
@@ -4426,11 +10162,11 @@
         <v>14</v>
       </c>
       <c r="G101" s="4">
-        <f t="shared" si="2"/>
+        <f>F101-E101</f>
         <v>5</v>
       </c>
       <c r="H101">
-        <f t="shared" si="3"/>
+        <f>IF(F101&gt;50,G101*0.2,G101*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I101" t="s">
@@ -4463,11 +10199,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G102" s="4">
-        <f t="shared" si="2"/>
+        <f>F102-E102</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H102">
-        <f t="shared" si="3"/>
+        <f>IF(F102&gt;50,G102*0.2,G102*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I102" t="s">
@@ -4500,11 +10236,11 @@
         <v>124</v>
       </c>
       <c r="G103" s="4">
-        <f t="shared" si="2"/>
+        <f>F103-E103</f>
         <v>64</v>
       </c>
       <c r="H103">
-        <f t="shared" si="3"/>
+        <f>IF(F103&gt;50,G103*0.2,G103*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I103" t="s">
@@ -4537,11 +10273,11 @@
         <v>16.3</v>
       </c>
       <c r="G104" s="4">
-        <f t="shared" si="2"/>
+        <f>F104-E104</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H104">
-        <f t="shared" si="3"/>
+        <f>IF(F104&gt;50,G104*0.2,G104*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I104" t="s">
@@ -4574,11 +10310,11 @@
         <v>16.3</v>
       </c>
       <c r="G105" s="4">
-        <f t="shared" si="2"/>
+        <f>F105-E105</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="H105">
-        <f t="shared" si="3"/>
+        <f>IF(F105&gt;50,G105*0.2,G105*0.1)</f>
         <v>0.49000000000000005</v>
       </c>
       <c r="I105" t="s">
@@ -4611,11 +10347,11 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="G106" s="4">
-        <f t="shared" si="2"/>
+        <f>F106-E106</f>
         <v>2.9999999999999991</v>
       </c>
       <c r="H106">
-        <f t="shared" si="3"/>
+        <f>IF(F106&gt;50,G106*0.2,G106*0.1)</f>
         <v>0.29999999999999993</v>
       </c>
       <c r="I106" t="s">
@@ -4648,11 +10384,11 @@
         <v>98.4</v>
       </c>
       <c r="G107" s="4">
-        <f t="shared" si="2"/>
+        <f>F107-E107</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H107">
-        <f t="shared" si="3"/>
+        <f>IF(F107&gt;50,G107*0.2,G107*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I107" t="s">
@@ -4685,11 +10421,11 @@
         <v>8</v>
       </c>
       <c r="G108" s="4">
-        <f t="shared" si="2"/>
+        <f>F108-E108</f>
         <v>5</v>
       </c>
       <c r="H108">
-        <f t="shared" si="3"/>
+        <f>IF(F108&gt;50,G108*0.2,G108*0.1)</f>
         <v>0.5</v>
       </c>
       <c r="I108" t="s">
@@ -4722,11 +10458,11 @@
         <v>98.4</v>
       </c>
       <c r="G109" s="4">
-        <f t="shared" si="2"/>
+        <f>F109-E109</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H109">
-        <f t="shared" si="3"/>
+        <f>IF(F109&gt;50,G109*0.2,G109*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I109" t="s">
@@ -4759,11 +10495,11 @@
         <v>502</v>
       </c>
       <c r="G110" s="4">
-        <f t="shared" si="2"/>
+        <f>F110-E110</f>
         <v>158</v>
       </c>
       <c r="H110">
-        <f t="shared" si="3"/>
+        <f>IF(F110&gt;50,G110*0.2,G110*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I110" t="s">
@@ -4796,11 +10532,11 @@
         <v>502</v>
       </c>
       <c r="G111" s="4">
-        <f t="shared" si="2"/>
+        <f>F111-E111</f>
         <v>158</v>
       </c>
       <c r="H111">
-        <f t="shared" si="3"/>
+        <f>IF(F111&gt;50,G111*0.2,G111*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I111" t="s">
@@ -4833,11 +10569,11 @@
         <v>77</v>
       </c>
       <c r="G112" s="4">
-        <f t="shared" si="2"/>
+        <f>F112-E112</f>
         <v>35</v>
       </c>
       <c r="H112">
-        <f t="shared" si="3"/>
+        <f>IF(F112&gt;50,G112*0.2,G112*0.1)</f>
         <v>7</v>
       </c>
       <c r="I112" t="s">
@@ -4870,11 +10606,11 @@
         <v>77</v>
       </c>
       <c r="G113" s="4">
-        <f t="shared" si="2"/>
+        <f>F113-E113</f>
         <v>35</v>
       </c>
       <c r="H113">
-        <f t="shared" si="3"/>
+        <f>IF(F113&gt;50,G113*0.2,G113*0.1)</f>
         <v>7</v>
       </c>
       <c r="I113" t="s">
@@ -4907,11 +10643,11 @@
         <v>98.4</v>
       </c>
       <c r="G114" s="4">
-        <f t="shared" si="2"/>
+        <f>F114-E114</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H114">
-        <f t="shared" si="3"/>
+        <f>IF(F114&gt;50,G114*0.2,G114*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I114" t="s">
@@ -4944,11 +10680,11 @@
         <v>124</v>
       </c>
       <c r="G115" s="4">
-        <f t="shared" si="2"/>
+        <f>F115-E115</f>
         <v>64</v>
       </c>
       <c r="H115">
-        <f t="shared" si="3"/>
+        <f>IF(F115&gt;50,G115*0.2,G115*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I115" t="s">
@@ -4981,11 +10717,11 @@
         <v>502</v>
       </c>
       <c r="G116" s="4">
-        <f t="shared" si="2"/>
+        <f>F116-E116</f>
         <v>158</v>
       </c>
       <c r="H116">
-        <f t="shared" si="3"/>
+        <f>IF(F116&gt;50,G116*0.2,G116*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I116" t="s">
@@ -5018,11 +10754,11 @@
         <v>77</v>
       </c>
       <c r="G117" s="4">
-        <f t="shared" si="2"/>
+        <f>F117-E117</f>
         <v>35</v>
       </c>
       <c r="H117">
-        <f t="shared" si="3"/>
+        <f>IF(F117&gt;50,G117*0.2,G117*0.1)</f>
         <v>7</v>
       </c>
       <c r="I117" t="s">
@@ -5055,11 +10791,11 @@
         <v>502</v>
       </c>
       <c r="G118" s="4">
-        <f t="shared" si="2"/>
+        <f>F118-E118</f>
         <v>158</v>
       </c>
       <c r="H118">
-        <f t="shared" si="3"/>
+        <f>IF(F118&gt;50,G118*0.2,G118*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I118" t="s">
@@ -5092,11 +10828,11 @@
         <v>98.4</v>
       </c>
       <c r="G119" s="4">
-        <f t="shared" si="2"/>
+        <f>F119-E119</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H119">
-        <f t="shared" si="3"/>
+        <f>IF(F119&gt;50,G119*0.2,G119*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I119" t="s">
@@ -5129,11 +10865,11 @@
         <v>124</v>
       </c>
       <c r="G120" s="4">
-        <f t="shared" si="2"/>
+        <f>F120-E120</f>
         <v>64</v>
       </c>
       <c r="H120">
-        <f t="shared" si="3"/>
+        <f>IF(F120&gt;50,G120*0.2,G120*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I120" t="s">
@@ -5166,11 +10902,11 @@
         <v>124</v>
       </c>
       <c r="G121" s="4">
-        <f t="shared" si="2"/>
+        <f>F121-E121</f>
         <v>64</v>
       </c>
       <c r="H121">
-        <f t="shared" si="3"/>
+        <f>IF(F121&gt;50,G121*0.2,G121*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I121" t="s">
@@ -5203,11 +10939,11 @@
         <v>87</v>
       </c>
       <c r="G122" s="4">
-        <f t="shared" si="2"/>
+        <f>F122-E122</f>
         <v>42</v>
       </c>
       <c r="H122">
-        <f t="shared" si="3"/>
+        <f>IF(F122&gt;50,G122*0.2,G122*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I122" t="s">
@@ -5240,11 +10976,11 @@
         <v>502</v>
       </c>
       <c r="G123" s="4">
-        <f t="shared" si="2"/>
+        <f>F123-E123</f>
         <v>158</v>
       </c>
       <c r="H123">
-        <f t="shared" si="3"/>
+        <f>IF(F123&gt;50,G123*0.2,G123*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I123" t="s">
@@ -5277,11 +11013,11 @@
         <v>98.4</v>
       </c>
       <c r="G124" s="4">
-        <f t="shared" si="2"/>
+        <f>F124-E124</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H124">
-        <f t="shared" si="3"/>
+        <f>IF(F124&gt;50,G124*0.2,G124*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I124" t="s">
@@ -5314,11 +11050,11 @@
         <v>87</v>
       </c>
       <c r="G125" s="4">
-        <f t="shared" si="2"/>
+        <f>F125-E125</f>
         <v>42</v>
       </c>
       <c r="H125">
-        <f t="shared" si="3"/>
+        <f>IF(F125&gt;50,G125*0.2,G125*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I125" t="s">
@@ -5351,11 +11087,11 @@
         <v>124</v>
       </c>
       <c r="G126" s="4">
-        <f t="shared" si="2"/>
+        <f>F126-E126</f>
         <v>64</v>
       </c>
       <c r="H126">
-        <f t="shared" si="3"/>
+        <f>IF(F126&gt;50,G126*0.2,G126*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I126" t="s">
@@ -5388,11 +11124,11 @@
         <v>7</v>
       </c>
       <c r="G127" s="4">
-        <f t="shared" si="2"/>
+        <f>F127-E127</f>
         <v>3</v>
       </c>
       <c r="H127">
-        <f t="shared" si="3"/>
+        <f>IF(F127&gt;50,G127*0.2,G127*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I127" t="s">
@@ -5425,11 +11161,11 @@
         <v>502</v>
       </c>
       <c r="G128" s="4">
-        <f t="shared" si="2"/>
+        <f>F128-E128</f>
         <v>158</v>
       </c>
       <c r="H128">
-        <f t="shared" si="3"/>
+        <f>IF(F128&gt;50,G128*0.2,G128*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I128" t="s">
@@ -5462,11 +11198,11 @@
         <v>77</v>
       </c>
       <c r="G129" s="4">
-        <f t="shared" si="2"/>
+        <f>F129-E129</f>
         <v>35</v>
       </c>
       <c r="H129">
-        <f t="shared" si="3"/>
+        <f>IF(F129&gt;50,G129*0.2,G129*0.1)</f>
         <v>7</v>
       </c>
       <c r="I129" t="s">
@@ -5499,11 +11235,11 @@
         <v>98.4</v>
       </c>
       <c r="G130" s="4">
-        <f t="shared" si="2"/>
+        <f>F130-E130</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H130">
-        <f t="shared" si="3"/>
+        <f>IF(F130&gt;50,G130*0.2,G130*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I130" t="s">
@@ -5536,11 +11272,11 @@
         <v>87</v>
       </c>
       <c r="G131" s="4">
-        <f t="shared" ref="G131:G172" si="4">F131-E131</f>
+        <f>F131-E131</f>
         <v>42</v>
       </c>
       <c r="H131">
-        <f t="shared" ref="H131:H172" si="5">IF(F131&gt;50,G131*0.2,G131*0.1)</f>
+        <f>IF(F131&gt;50,G131*0.2,G131*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I131" t="s">
@@ -5573,11 +11309,11 @@
         <v>7</v>
       </c>
       <c r="G132" s="4">
-        <f t="shared" si="4"/>
+        <f>F132-E132</f>
         <v>3</v>
       </c>
       <c r="H132">
-        <f t="shared" si="5"/>
+        <f>IF(F132&gt;50,G132*0.2,G132*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I132" t="s">
@@ -5610,11 +11346,11 @@
         <v>7</v>
       </c>
       <c r="G133" s="4">
-        <f t="shared" si="4"/>
+        <f>F133-E133</f>
         <v>3</v>
       </c>
       <c r="H133">
-        <f t="shared" si="5"/>
+        <f>IF(F133&gt;50,G133*0.2,G133*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I133" t="s">
@@ -5647,11 +11383,11 @@
         <v>98.4</v>
       </c>
       <c r="G134" s="4">
-        <f t="shared" si="4"/>
+        <f>F134-E134</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H134">
-        <f t="shared" si="5"/>
+        <f>IF(F134&gt;50,G134*0.2,G134*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I134" t="s">
@@ -5684,11 +11420,11 @@
         <v>98.4</v>
       </c>
       <c r="G135" s="4">
-        <f t="shared" si="4"/>
+        <f>F135-E135</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H135">
-        <f t="shared" si="5"/>
+        <f>IF(F135&gt;50,G135*0.2,G135*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I135" t="s">
@@ -5721,11 +11457,11 @@
         <v>502</v>
       </c>
       <c r="G136" s="4">
-        <f t="shared" si="4"/>
+        <f>F136-E136</f>
         <v>158</v>
       </c>
       <c r="H136">
-        <f t="shared" si="5"/>
+        <f>IF(F136&gt;50,G136*0.2,G136*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I136" t="s">
@@ -5758,11 +11494,11 @@
         <v>124</v>
       </c>
       <c r="G137" s="4">
-        <f t="shared" si="4"/>
+        <f>F137-E137</f>
         <v>64</v>
       </c>
       <c r="H137">
-        <f t="shared" si="5"/>
+        <f>IF(F137&gt;50,G137*0.2,G137*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I137" t="s">
@@ -5795,11 +11531,11 @@
         <v>98.4</v>
       </c>
       <c r="G138" s="4">
-        <f t="shared" si="4"/>
+        <f>F138-E138</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H138">
-        <f t="shared" si="5"/>
+        <f>IF(F138&gt;50,G138*0.2,G138*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I138" t="s">
@@ -5832,11 +11568,11 @@
         <v>502</v>
       </c>
       <c r="G139" s="4">
-        <f t="shared" si="4"/>
+        <f>F139-E139</f>
         <v>158</v>
       </c>
       <c r="H139">
-        <f t="shared" si="5"/>
+        <f>IF(F139&gt;50,G139*0.2,G139*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I139" t="s">
@@ -5869,11 +11605,11 @@
         <v>87</v>
       </c>
       <c r="G140" s="4">
-        <f t="shared" si="4"/>
+        <f>F140-E140</f>
         <v>42</v>
       </c>
       <c r="H140">
-        <f t="shared" si="5"/>
+        <f>IF(F140&gt;50,G140*0.2,G140*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I140" t="s">
@@ -5906,11 +11642,11 @@
         <v>87</v>
       </c>
       <c r="G141" s="4">
-        <f t="shared" si="4"/>
+        <f>F141-E141</f>
         <v>42</v>
       </c>
       <c r="H141">
-        <f t="shared" si="5"/>
+        <f>IF(F141&gt;50,G141*0.2,G141*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I141" t="s">
@@ -5943,11 +11679,11 @@
         <v>7</v>
       </c>
       <c r="G142" s="4">
-        <f t="shared" si="4"/>
+        <f>F142-E142</f>
         <v>3</v>
       </c>
       <c r="H142">
-        <f t="shared" si="5"/>
+        <f>IF(F142&gt;50,G142*0.2,G142*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I142" t="s">
@@ -5980,11 +11716,11 @@
         <v>124</v>
       </c>
       <c r="G143" s="4">
-        <f t="shared" si="4"/>
+        <f>F143-E143</f>
         <v>64</v>
       </c>
       <c r="H143">
-        <f t="shared" si="5"/>
+        <f>IF(F143&gt;50,G143*0.2,G143*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I143" t="s">
@@ -6017,11 +11753,11 @@
         <v>98.4</v>
       </c>
       <c r="G144" s="4">
-        <f t="shared" si="4"/>
+        <f>F144-E144</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H144">
-        <f t="shared" si="5"/>
+        <f>IF(F144&gt;50,G144*0.2,G144*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I144" t="s">
@@ -6054,11 +11790,11 @@
         <v>124</v>
       </c>
       <c r="G145" s="4">
-        <f t="shared" si="4"/>
+        <f>F145-E145</f>
         <v>64</v>
       </c>
       <c r="H145">
-        <f t="shared" si="5"/>
+        <f>IF(F145&gt;50,G145*0.2,G145*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I145" t="s">
@@ -6091,11 +11827,11 @@
         <v>87</v>
       </c>
       <c r="G146" s="4">
-        <f t="shared" si="4"/>
+        <f>F146-E146</f>
         <v>42</v>
       </c>
       <c r="H146">
-        <f t="shared" si="5"/>
+        <f>IF(F146&gt;50,G146*0.2,G146*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I146" t="s">
@@ -6128,11 +11864,11 @@
         <v>502</v>
       </c>
       <c r="G147" s="4">
-        <f t="shared" si="4"/>
+        <f>F147-E147</f>
         <v>158</v>
       </c>
       <c r="H147">
-        <f t="shared" si="5"/>
+        <f>IF(F147&gt;50,G147*0.2,G147*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I147" t="s">
@@ -6165,11 +11901,11 @@
         <v>98.4</v>
       </c>
       <c r="G148" s="4">
-        <f t="shared" si="4"/>
+        <f>F148-E148</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H148">
-        <f t="shared" si="5"/>
+        <f>IF(F148&gt;50,G148*0.2,G148*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I148" t="s">
@@ -6202,11 +11938,11 @@
         <v>7</v>
       </c>
       <c r="G149" s="4">
-        <f t="shared" si="4"/>
+        <f>F149-E149</f>
         <v>3</v>
       </c>
       <c r="H149">
-        <f t="shared" si="5"/>
+        <f>IF(F149&gt;50,G149*0.2,G149*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I149" t="s">
@@ -6239,11 +11975,11 @@
         <v>502</v>
       </c>
       <c r="G150" s="4">
-        <f t="shared" si="4"/>
+        <f>F150-E150</f>
         <v>158</v>
       </c>
       <c r="H150">
-        <f t="shared" si="5"/>
+        <f>IF(F150&gt;50,G150*0.2,G150*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I150" t="s">
@@ -6276,11 +12012,11 @@
         <v>124</v>
       </c>
       <c r="G151" s="4">
-        <f t="shared" si="4"/>
+        <f>F151-E151</f>
         <v>64</v>
       </c>
       <c r="H151">
-        <f t="shared" si="5"/>
+        <f>IF(F151&gt;50,G151*0.2,G151*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I151" t="s">
@@ -6313,11 +12049,11 @@
         <v>124</v>
       </c>
       <c r="G152" s="4">
-        <f t="shared" si="4"/>
+        <f>F152-E152</f>
         <v>64</v>
       </c>
       <c r="H152">
-        <f t="shared" si="5"/>
+        <f>IF(F152&gt;50,G152*0.2,G152*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I152" t="s">
@@ -6350,11 +12086,11 @@
         <v>87</v>
       </c>
       <c r="G153" s="4">
-        <f t="shared" si="4"/>
+        <f>F153-E153</f>
         <v>42</v>
       </c>
       <c r="H153">
-        <f t="shared" si="5"/>
+        <f>IF(F153&gt;50,G153*0.2,G153*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I153" t="s">
@@ -6387,11 +12123,11 @@
         <v>502</v>
       </c>
       <c r="G154" s="4">
-        <f t="shared" si="4"/>
+        <f>F154-E154</f>
         <v>158</v>
       </c>
       <c r="H154">
-        <f t="shared" si="5"/>
+        <f>IF(F154&gt;50,G154*0.2,G154*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I154" t="s">
@@ -6424,11 +12160,11 @@
         <v>98.4</v>
       </c>
       <c r="G155" s="4">
-        <f t="shared" si="4"/>
+        <f>F155-E155</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H155">
-        <f t="shared" si="5"/>
+        <f>IF(F155&gt;50,G155*0.2,G155*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I155" t="s">
@@ -6461,11 +12197,11 @@
         <v>87</v>
       </c>
       <c r="G156" s="4">
-        <f t="shared" si="4"/>
+        <f>F156-E156</f>
         <v>42</v>
       </c>
       <c r="H156">
-        <f t="shared" si="5"/>
+        <f>IF(F156&gt;50,G156*0.2,G156*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I156" t="s">
@@ -6498,11 +12234,11 @@
         <v>124</v>
       </c>
       <c r="G157" s="4">
-        <f t="shared" si="4"/>
+        <f>F157-E157</f>
         <v>64</v>
       </c>
       <c r="H157">
-        <f t="shared" si="5"/>
+        <f>IF(F157&gt;50,G157*0.2,G157*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I157" t="s">
@@ -6535,11 +12271,11 @@
         <v>7</v>
       </c>
       <c r="G158" s="4">
-        <f t="shared" si="4"/>
+        <f>F158-E158</f>
         <v>3</v>
       </c>
       <c r="H158">
-        <f t="shared" si="5"/>
+        <f>IF(F158&gt;50,G158*0.2,G158*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I158" t="s">
@@ -6572,11 +12308,11 @@
         <v>502</v>
       </c>
       <c r="G159" s="4">
-        <f t="shared" si="4"/>
+        <f>F159-E159</f>
         <v>158</v>
       </c>
       <c r="H159">
-        <f t="shared" si="5"/>
+        <f>IF(F159&gt;50,G159*0.2,G159*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I159" t="s">
@@ -6609,11 +12345,11 @@
         <v>77</v>
       </c>
       <c r="G160" s="4">
-        <f t="shared" si="4"/>
+        <f>F160-E160</f>
         <v>35</v>
       </c>
       <c r="H160">
-        <f t="shared" si="5"/>
+        <f>IF(F160&gt;50,G160*0.2,G160*0.1)</f>
         <v>7</v>
       </c>
       <c r="I160" t="s">
@@ -6626,7 +12362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:13">
       <c r="A161" s="1" t="s">
         <v>29</v>
       </c>
@@ -6646,11 +12382,11 @@
         <v>98.4</v>
       </c>
       <c r="G161" s="4">
-        <f t="shared" si="4"/>
+        <f>F161-E161</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H161">
-        <f t="shared" si="5"/>
+        <f>IF(F161&gt;50,G161*0.2,G161*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I161" t="s">
@@ -6663,7 +12399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:13">
       <c r="A162" s="1" t="s">
         <v>29</v>
       </c>
@@ -6683,11 +12419,11 @@
         <v>87</v>
       </c>
       <c r="G162" s="4">
-        <f t="shared" si="4"/>
+        <f>F162-E162</f>
         <v>42</v>
       </c>
       <c r="H162">
-        <f t="shared" si="5"/>
+        <f>IF(F162&gt;50,G162*0.2,G162*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I162" t="s">
@@ -6700,7 +12436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:13">
       <c r="A163" s="1" t="s">
         <v>29</v>
       </c>
@@ -6720,11 +12456,11 @@
         <v>7</v>
       </c>
       <c r="G163" s="4">
-        <f t="shared" si="4"/>
+        <f>F163-E163</f>
         <v>3</v>
       </c>
       <c r="H163">
-        <f t="shared" si="5"/>
+        <f>IF(F163&gt;50,G163*0.2,G163*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I163" t="s">
@@ -6737,7 +12473,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:13">
       <c r="A164" s="1" t="s">
         <v>29</v>
       </c>
@@ -6757,11 +12493,11 @@
         <v>7</v>
       </c>
       <c r="G164" s="4">
-        <f t="shared" si="4"/>
+        <f>F164-E164</f>
         <v>3</v>
       </c>
       <c r="H164">
-        <f t="shared" si="5"/>
+        <f>IF(F164&gt;50,G164*0.2,G164*0.1)</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="I164" t="s">
@@ -6774,7 +12510,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:13">
       <c r="A165" s="1" t="s">
         <v>29</v>
       </c>
@@ -6794,11 +12530,11 @@
         <v>98.4</v>
       </c>
       <c r="G165" s="4">
-        <f t="shared" si="4"/>
+        <f>F165-E165</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H165">
-        <f t="shared" si="5"/>
+        <f>IF(F165&gt;50,G165*0.2,G165*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I165" t="s">
@@ -6811,7 +12547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:13">
       <c r="A166" s="1" t="s">
         <v>29</v>
       </c>
@@ -6831,11 +12567,11 @@
         <v>98.4</v>
       </c>
       <c r="G166" s="4">
-        <f t="shared" si="4"/>
+        <f>F166-E166</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H166">
-        <f t="shared" si="5"/>
+        <f>IF(F166&gt;50,G166*0.2,G166*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I166" t="s">
@@ -6847,8 +12583,11 @@
       <c r="K166" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="167" spans="1:11">
+      <c r="L166" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167" s="1" t="s">
         <v>29</v>
       </c>
@@ -6868,11 +12607,11 @@
         <v>502</v>
       </c>
       <c r="G167" s="4">
-        <f t="shared" si="4"/>
+        <f>F167-E167</f>
         <v>158</v>
       </c>
       <c r="H167">
-        <f t="shared" si="5"/>
+        <f>IF(F167&gt;50,G167*0.2,G167*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I167" t="s">
@@ -6884,8 +12623,11 @@
       <c r="K167" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="168" spans="1:11">
+      <c r="L167" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168" s="1" t="s">
         <v>30</v>
       </c>
@@ -6905,11 +12647,11 @@
         <v>124</v>
       </c>
       <c r="G168" s="4">
-        <f t="shared" si="4"/>
+        <f>F168-E168</f>
         <v>64</v>
       </c>
       <c r="H168">
-        <f t="shared" si="5"/>
+        <f>IF(F168&gt;50,G168*0.2,G168*0.1)</f>
         <v>12.8</v>
       </c>
       <c r="I168" t="s">
@@ -6921,8 +12663,11 @@
       <c r="K168" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="169" spans="1:11">
+      <c r="L168" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169" s="1" t="s">
         <v>30</v>
       </c>
@@ -6942,11 +12687,11 @@
         <v>98.4</v>
       </c>
       <c r="G169" s="4">
-        <f t="shared" si="4"/>
+        <f>F169-E169</f>
         <v>40.100000000000009</v>
       </c>
       <c r="H169">
-        <f t="shared" si="5"/>
+        <f>IF(F169&gt;50,G169*0.2,G169*0.1)</f>
         <v>8.0200000000000014</v>
       </c>
       <c r="I169" t="s">
@@ -6958,8 +12703,14 @@
       <c r="K169" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="170" spans="1:11">
+      <c r="L169" t="s">
+        <v>53</v>
+      </c>
+      <c r="M169" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170" s="1" t="s">
         <v>30</v>
       </c>
@@ -6979,11 +12730,11 @@
         <v>502</v>
       </c>
       <c r="G170" s="4">
-        <f t="shared" si="4"/>
+        <f>F170-E170</f>
         <v>158</v>
       </c>
       <c r="H170">
-        <f t="shared" si="5"/>
+        <f>IF(F170&gt;50,G170*0.2,G170*0.1)</f>
         <v>31.6</v>
       </c>
       <c r="I170" t="s">
@@ -6995,8 +12746,11 @@
       <c r="K170" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="171" spans="1:11">
+      <c r="L170" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171" s="1" t="s">
         <v>30</v>
       </c>
@@ -7016,11 +12770,11 @@
         <v>87</v>
       </c>
       <c r="G171" s="4">
-        <f t="shared" si="4"/>
+        <f>F171-E171</f>
         <v>42</v>
       </c>
       <c r="H171">
-        <f t="shared" si="5"/>
+        <f>IF(F171&gt;50,G171*0.2,G171*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I171" t="s">
@@ -7033,7 +12787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:13">
       <c r="A172" s="1" t="s">
         <v>30</v>
       </c>
@@ -7053,11 +12807,11 @@
         <v>87</v>
       </c>
       <c r="G172" s="4">
-        <f t="shared" si="4"/>
+        <f>F172-E172</f>
         <v>42</v>
       </c>
       <c r="H172">
-        <f t="shared" si="5"/>
+        <f>IF(F172&gt;50,G172*0.2,G172*0.1)</f>
         <v>8.4</v>
       </c>
       <c r="I172" t="s">
@@ -7070,7 +12824,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:13">
       <c r="A174" s="1" t="s">
         <v>47</v>
       </c>
@@ -7079,7 +12833,7 @@
         <v>17110.599999999995</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:13">
       <c r="A175" s="1" t="s">
         <v>48</v>
       </c>
@@ -7088,7 +12842,7 @@
         <v>16088.399999999994</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:13">
       <c r="A176" s="1" t="s">
         <v>49</v>
       </c>
@@ -7098,11 +12852,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L172" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate topLabels="1">
     <dataRefs count="1">
       <dataRef ref="A2:G59" sheet="Sales"/>
     </dataRefs>
   </dataConsolidate>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
   <extLst>
